--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261013.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20261013.xlsx
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>266,120,250</t>
+          <t>8,552,572</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,17 +997,17 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>8,552,572</t>
+          <t>266,120,250</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>7,194,072</t>
+          <t>2,181,010</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>2,181,010</t>
+          <t>7,194,072</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>2,022,445</t>
+          <t>365,463,477</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>365,463,477</t>
+          <t>2,022,445</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>70,078,114</t>
+          <t>88,591,503</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>88,591,503</t>
+          <t>70,078,114</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>4,150,890</t>
+          <t>8,078,818</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>8,078,818</t>
+          <t>4,150,890</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>249,882,907</t>
+          <t>25,300,942</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>25,300,942</t>
+          <t>249,882,907</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
